--- a/results/reliability_eval/Llama-3-8B_toy-qa-dataset_sample_15_tokens_0.1_temp_deductive_reasoning_raw_table_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_toy-qa-dataset_sample_15_tokens_0.1_temp_deductive_reasoning_raw_table_08-24-4.xlsx
@@ -494,24 +494,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the location of the Great Wall of China?.://www.google.com/url?sa=U&amp;ved=0</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.3256774246692657</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.9279384613037109</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0.6258097887039185</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 0.6514), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 1.0), ('sa', 1.0), ('=', 0.5), ('U', 1.0), ('&amp;', 1.0), ('ved', 1.0), ('=', 1.0), ('0', 1.0)]</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -532,24 +532,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the location of the Great Wall of China?.://en.wikipedia.org/wiki/China
+Given these facts:</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.1215534284710884</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.868929386138916</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0.7347352504730225</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.3486), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('China', 0.3486), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -570,24 +571,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the location of the Great Wall of China?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.2270916998386383</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.9058996438980103</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0.6466038227081299</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.3486), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 0.6514), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -608,24 +610,24 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the location of the Great Wall of China?.://www.google.com/url?sa=U&amp;ved=0</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0.3256774246692657</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.9279384613037109</v>
       </c>
       <c r="G5" t="n">
-        <v>-0</v>
+        <v>0.6258097887039185</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 0.6514), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 1.0), ('sa', 1.0), ('=', 0.5), ('U', 1.0), ('&amp;', 1.0), ('ved', 1.0), ('=', 1.0), ('0', 1.0)]</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -646,24 +648,24 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the location of the Great Wall of China?.://www.google.com/url?sa=U&amp;ved=0</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0.3256774246692657</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.9279384613037109</v>
       </c>
       <c r="G6" t="n">
-        <v>-0</v>
+        <v>0.6258097887039185</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 0.6514), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 1.0), ('sa', 1.0), ('=', 0.5), ('U', 1.0), ('&amp;', 1.0), ('ved', 1.0), ('=', 1.0), ('0', 1.0)]</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -684,24 +686,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the location of the Great Wall of China?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0.2270916998386383</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.9058996438980103</v>
       </c>
       <c r="G7" t="n">
-        <v>-0</v>
+        <v>0.6466038227081299</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.3486), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 0.6514), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -722,24 +725,24 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the location of the Great Wall of China?.://www.google.com/url?sa=U&amp;ved=0</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0.3256774246692657</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0.9279384613037109</v>
       </c>
       <c r="G8" t="n">
-        <v>-0</v>
+        <v>0.6258097887039185</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 0.6514), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 1.0), ('sa', 1.0), ('=', 0.5), ('U', 1.0), ('&amp;', 1.0), ('ved', 1.0), ('=', 1.0), ('0', 1.0)]</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -760,24 +763,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the location of the Great Wall of China?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0.2270916998386383</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0.9058996438980103</v>
       </c>
       <c r="G9" t="n">
-        <v>-0</v>
+        <v>0.6466038227081299</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.3486), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 0.6514), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -798,24 +802,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the location of the Great Wall of China?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0.2270916998386383</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0.9058996438980103</v>
       </c>
       <c r="G10" t="n">
-        <v>-0</v>
+        <v>0.6466038227081299</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.3486), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 0.6514), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -836,24 +841,24 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the location of the Great Wall of China?.://www.google.com/url?sa=t&amp;source=web&amp;r</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0.3256774246692657</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0.9279384613037109</v>
       </c>
       <c r="G11" t="n">
-        <v>-0</v>
+        <v>0.6258097887039185</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 0.6514), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 1.0), ('sa', 1.0), ('=t', 0.5), ('&amp;', 1.0), ('source', 1.0), ('=', 1.0), ('web', 1.0), ('&amp;r', 1.0)]</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -874,24 +879,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Where is the Eiffel Tower located?.://en.wikipedia.org/wiki/Eiffel_Tower
+Given these</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G12" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.3486), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/E', 1.0), ('iff', 1.0), ('el', 1.0), ('_T', 1.0), ('ower', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0)]</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -912,24 +918,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Where is the Eiffel Tower located?.://en.wikipedia.org/wiki/Eiffel_Tower
+Given these</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G13" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.3486), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/E', 1.0), ('iff', 1.0), ('el', 1.0), ('_T', 1.0), ('ower', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0)]</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -950,24 +957,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Where is the Eiffel Tower located?.://en.wikipedia.org/wiki/Eiffel_Tower
+Given these</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G14" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.3486), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/E', 1.0), ('iff', 1.0), ('el', 1.0), ('_T', 1.0), ('ower', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0)]</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -988,24 +996,24 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Where is the Eiffel Tower located?.://www.://www. is the Eiffel</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.2121315747499466</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0.901793360710144</v>
       </c>
       <c r="G15" t="n">
-        <v>-0</v>
+        <v>0.9050460457801819</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 0.6514), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), (' is', 0.6514), (' the', 1.0), (' E', 0.5), ('iff', 1.0), ('el', 1.0)]</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1026,24 +1034,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Where is the Eiffel Tower located?.://en.wikipedia.org/wiki/Eiffel_Tower
+Given these</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G16" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.3486), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/E', 1.0), ('iff', 1.0), ('el', 1.0), ('_T', 1.0), ('ower', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0)]</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1064,24 +1073,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Where is the Eiffel Tower located?.://en.wikipedia.org/wiki/Eiffel_Tower
+Given these</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G17" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.3486), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/E', 1.0), ('iff', 1.0), ('el', 1.0), ('_T', 1.0), ('ower', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0)]</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1102,24 +1112,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Where is the Eiffel Tower located?.://www.://www. is the answer.
+Given</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0.1060657873749733</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0.8610697984695435</v>
       </c>
       <c r="G18" t="n">
-        <v>-0</v>
+        <v>1.251619577407837</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 0.6514), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), (' is', 0.6514), (' the', 1.0), (' answer', 0.5), ('.\n', 0.5), ('Given', 1.0)]</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1140,24 +1151,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Where is the Eiffel Tower located?.://www.://www. is the answer.
+Given</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0.1060657873749733</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0.8610697984695435</v>
       </c>
       <c r="G19" t="n">
-        <v>-0</v>
+        <v>1.251619577407837</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 0.6514), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), (' is', 0.6514), (' the', 1.0), (' answer', 0.5), ('.\n', 0.5), ('Given', 1.0)]</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1178,24 +1190,24 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Where is the Eiffel Tower located?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0.2270916998386383</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0.9058996438980103</v>
       </c>
       <c r="G20" t="n">
-        <v>-0</v>
+        <v>0.6466038227081299</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 0.6514), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 0.3486), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1216,24 +1228,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Where is the Eiffel Tower located?.://en.wikipedia.org/wiki/Eiffel_Tower
+Given these</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G21" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.3486), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/E', 1.0), ('iff', 1.0), ('el', 1.0), ('_T', 1.0), ('ower', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0)]</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1254,28 +1267,29 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is the largest city in Japan</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the capital city of Japan?.://www.google.com/ is the capital city of Japan.
+Given</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9389386773109436</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' largest', 1.0), (' city', 1.0), (' in', 1.0), (' Japan', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.\n', 1.0), ('Given', 1.0)]</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1292,28 +1306,29 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is located on the eastern side</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the capital city of Japan?.://www.google.com/ is the capital city of Japan.
+Given</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9389386773109436</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 0.5), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.\n', 1.0), ('Given', 1.0)]</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1330,30 +1345,29 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo
-What is the capital city of Japan? Tokyo
-What is the</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the capital city of Japan?.://www.google.com/ is the capital city of Japan.
+Given</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.2227001488208771</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9047210812568665</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>0.334479808807373</v>
+        <v>-0</v>
       </c>
       <c r="H24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), ('\n', 0.2227), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('?', 1.0), (' Tokyo', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.\n', 1.0), ('Given', 1.0)]</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1370,28 +1384,29 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is located on the eastern side</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the capital city of Japan?.://www.google.com/ is the capital city of Japan.
+Given</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9389386773109436</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 0.5), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.\n', 1.0), ('Given', 1.0)]</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1408,28 +1423,29 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is the largest city in Japan</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the capital city of Japan?.://www.google.com/ is the capital city of Japan.
+Given</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9389386773109436</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' largest', 1.0), (' city', 1.0), (' in', 1.0), (' Japan', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.\n', 1.0), ('Given', 1.0)]</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1446,28 +1462,29 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is located on the eastern side</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the capital city of Japan?.://www.google.com/ is the capital city of Japan.
+Given</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9389386773109436</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 0.5), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.\n', 1.0), ('Given', 1.0)]</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1484,28 +1501,29 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is the largest city in Japan</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the capital city of Japan?.://www.google.com/ is the capital city of Japan.
+Given</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9389386773109436</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' largest', 1.0), (' city', 1.0), (' in', 1.0), (' Japan', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.\n', 1.0), ('Given', 1.0)]</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1522,28 +1540,29 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is the largest city in Japan</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the capital city of Japan?.://www.google.com/ is the capital city of Japan.
+Given</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9389386773109436</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' largest', 1.0), (' city', 1.0), (' in', 1.0), (' Japan', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.\n', 1.0), ('Given', 1.0)]</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1560,28 +1579,29 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is located on the eastern side</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the capital city of Japan?.://www.google.com/ is the capital city of Japan.
+Given</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9389386773109436</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 0.5), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.\n', 1.0), ('Given', 1.0)]</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1598,28 +1618,29 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is located on the eastern side</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the capital city of Japan?.://www.google.com/ is the capital city of Japan.
+Given</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9389386773109436</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 0.5), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.\n', 1.0), ('Given', 1.0)]</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1636,28 +1657,29 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? Is it sour? Is it bitter? Is it sweet? Is it salty</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How would you describe the taste of a lemon?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.7772998809814453</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9833449721336365</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1958244144916534</v>
+        <v>-0</v>
       </c>
       <c r="H32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>[(' Is', 0.7773), (' it', 1.0), (' sour', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' bitter', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' sweet', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' salty', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1674,28 +1696,29 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? What about the smell of a rose? The answer to these questions is subjective</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How would you describe the taste of a lemon?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.1450568288564682</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8792300820350647</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>0.6137160062789917</v>
+        <v>-0</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>[(' What', 0.2227), (' about', 1.0), (' the', 1.0), (' smell', 1.0), (' of', 1.0), (' a', 1.0), (' rose', 1.0), ('?', 1.0), (' The', 0.6514), (' answer', 1.0), (' to', 1.0), (' these', 1.0), (' questions', 1.0), (' is', 1.0), (' subjective', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1712,28 +1735,29 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? Is it sour? Is it bitter? Is it sweet? Is it salty</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How would you describe the taste of a lemon?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.7772998809814453</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9833449721336365</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1958244144916534</v>
+        <v>-0</v>
       </c>
       <c r="H34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>[(' Is', 0.7773), (' it', 1.0), (' sour', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' bitter', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' sweet', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' salty', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1750,28 +1774,29 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? Is it sour? Is it bitter? Is it sweet? Is it salty</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How would you describe the taste of a lemon?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.7772998809814453</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9833449721336365</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1958244144916534</v>
+        <v>-0</v>
       </c>
       <c r="H35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>[(' Is', 0.7773), (' it', 1.0), (' sour', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' bitter', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' sweet', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' salty', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1788,28 +1813,29 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? What about the smell of a rose? The answer to these questions is subjective</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How would you describe the taste of a lemon?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.1450568288564682</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8792300820350647</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0.6137160062789917</v>
+        <v>-0</v>
       </c>
       <c r="H36" t="b">
         <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>[(' What', 0.2227), (' about', 1.0), (' the', 1.0), (' smell', 1.0), (' of', 1.0), (' a', 1.0), (' rose', 1.0), ('?', 1.0), (' The', 0.6514), (' answer', 1.0), (' to', 1.0), (' these', 1.0), (' questions', 1.0), (' is', 1.0), (' subjective', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1826,28 +1852,29 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? Is it sour? Is it bitter? Is it sweet? Is it salty</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How would you describe the taste of a lemon?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.7772998809814453</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9833449721336365</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>0.1958244144916534</v>
+        <v>-0</v>
       </c>
       <c r="H37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>[(' Is', 0.7773), (' it', 1.0), (' sour', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' bitter', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' sweet', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' salty', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1864,28 +1891,29 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? Is it sour? Is it bitter? Is it sweet? Is it salty</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How would you describe the taste of a lemon?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.7772998809814453</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9833449721336365</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1958244144916534</v>
+        <v>-0</v>
       </c>
       <c r="H38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>[(' Is', 0.7773), (' it', 1.0), (' sour', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' bitter', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' sweet', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' salty', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1902,28 +1930,29 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? What about the smell of a rose? What about the sound of a bird</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How would you describe the taste of a lemon?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.07764331996440887</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8433482646942139</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0.7018474340438843</v>
+        <v>-0</v>
       </c>
       <c r="H39" t="b">
         <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>[(' What', 0.2227), (' about', 1.0), (' the', 1.0), (' smell', 1.0), (' of', 1.0), (' a', 1.0), (' rose', 1.0), ('?', 1.0), (' What', 0.3486), (' about', 1.0), (' the', 1.0), (' sound', 1.0), (' of', 1.0), (' a', 1.0), (' bird', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1940,28 +1969,29 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? Is it sour? Is it bitter? Is it sweet? Is it salty</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How would you describe the taste of a lemon?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.7772998809814453</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9833449721336365</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1958244144916534</v>
+        <v>-0</v>
       </c>
       <c r="H40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>[(' Is', 0.7773), (' it', 1.0), (' sour', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' bitter', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' sweet', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' salty', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1978,28 +2008,29 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? What about the smell of a rose? The answer to these questions is subjective</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How would you describe the taste of a lemon?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.1450568288564682</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8792300820350647</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>0.6137160062789917</v>
+        <v>-0</v>
       </c>
       <c r="H41" t="b">
         <v>0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>[(' What', 0.2227), (' about', 1.0), (' the', 1.0), (' smell', 1.0), (' of', 1.0), (' a', 1.0), (' rose', 1.0), ('?', 1.0), (' The', 0.6514), (' answer', 1.0), (' to', 1.0), (' these', 1.0), (' questions', 1.0), (' is', 1.0), (' subjective', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2016,24 +2047,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The weather is clear. What is the best way to describe the weather on</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the best way to describe the weather on a clear day?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.7772998809814453</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9833449721336365</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>0.1958244144916534</v>
+        <v>-0</v>
       </c>
       <c r="H42" t="b">
         <v>0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' weather', 0.7773), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -2054,24 +2086,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The weather is clear. What is the best way to describe the weather on</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the best way to describe the weather on a clear day?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.7772998809814453</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9833449721336365</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1958244144916534</v>
+        <v>-0</v>
       </c>
       <c r="H43" t="b">
         <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' weather', 0.7773), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -2092,24 +2125,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The sky is blue, the sun is shining, and the air is crisp</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the best way to describe the weather on a clear day?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.2227001488208771</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9047210812568665</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>0.334479808807373</v>
+        <v>-0</v>
       </c>
       <c r="H44" t="b">
         <v>0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' sky', 0.2227), (' is', 1.0), (' blue', 1.0), (',', 1.0), (' the', 1.0), (' sun', 1.0), (' is', 1.0), (' shining', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' air', 1.0), (' is', 1.0), (' crisp', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -2130,24 +2164,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The sky is blue, the sun is shining, and the air is crisp</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the best way to describe the weather on a clear day?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.2227001488208771</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9047210812568665</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0.334479808807373</v>
+        <v>-0</v>
       </c>
       <c r="H45" t="b">
         <v>0</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' sky', 0.2227), (' is', 1.0), (' blue', 1.0), (',', 1.0), (' the', 1.0), (' sun', 1.0), (' is', 1.0), (' shining', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' air', 1.0), (' is', 1.0), (' crisp', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J45" t="n">
@@ -2168,24 +2203,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The sky is blue, the sun is shining, and the air is crisp</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the best way to describe the weather on a clear day?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.2227001488208771</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9047210812568665</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>0.334479808807373</v>
+        <v>-0</v>
       </c>
       <c r="H46" t="b">
         <v>0</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' sky', 0.2227), (' is', 1.0), (' blue', 1.0), (',', 1.0), (' the', 1.0), (' sun', 1.0), (' is', 1.0), (' shining', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' air', 1.0), (' is', 1.0), (' crisp', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -2206,24 +2242,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The weather is clear. What is the best way to describe the weather on</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the best way to describe the weather on a clear day?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.7772998809814453</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9833449721336365</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1958244144916534</v>
+        <v>-0</v>
       </c>
       <c r="H47" t="b">
         <v>0</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' weather', 0.7773), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -2244,24 +2281,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The weather is clear. What is the best way to describe the weather on</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the best way to describe the weather on a clear day?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.7772998809814453</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9833449721336365</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1958244144916534</v>
+        <v>-0</v>
       </c>
       <c r="H48" t="b">
         <v>0</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' weather', 0.7773), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -2282,24 +2320,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The weather is clear. What is the best way to describe the weather on</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the best way to describe the weather on a clear day?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.7772998809814453</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9833449721336365</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1958244144916534</v>
+        <v>-0</v>
       </c>
       <c r="H49" t="b">
         <v>0</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' weather', 0.7773), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -2320,24 +2359,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The weather is clear. What is the best way to describe the weather on</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the best way to describe the weather on a clear day?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.7772998809814453</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9833449721336365</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1958244144916534</v>
+        <v>-0</v>
       </c>
       <c r="H50" t="b">
         <v>0</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' weather', 0.7773), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J50" t="n">
@@ -2358,24 +2398,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The sky is blue, the sun is shining, and the air is crisp</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the best way to describe the weather on a clear day?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.2227001488208771</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9047210812568665</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>0.334479808807373</v>
+        <v>-0</v>
       </c>
       <c r="H51" t="b">
         <v>0</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' sky', 0.2227), (' is', 1.0), (' blue', 1.0), (',', 1.0), (' the', 1.0), (' sun', 1.0), (' is', 1.0), (' shining', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' air', 1.0), (' is', 1.0), (' crisp', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J51" t="n">
@@ -2396,28 +2437,28 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that’s</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How would you describe the feeling of touching velvet?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.424263209104538</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9444428682327271</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>0.5584724545478821</v>
+        <v>-0</v>
       </c>
       <c r="H52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), ('’s', 0.6514)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -2434,28 +2475,28 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that’s</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How would you describe the feeling of touching velvet?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.424263209104538</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9444428682327271</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>0.5584724545478821</v>
+        <v>-0</v>
       </c>
       <c r="H53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), ('’s', 0.6514)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2472,28 +2513,28 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that’s</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How would you describe the feeling of touching velvet?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.424263209104538</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9444428682327271</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0.5584724545478821</v>
+        <v>-0</v>
       </c>
       <c r="H54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), ('’s', 0.6514)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2510,28 +2551,28 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that’s</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How would you describe the feeling of touching velvet?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.424263209104538</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9444428682327271</v>
+        <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>0.5584724545478821</v>
+        <v>-0</v>
       </c>
       <c r="H55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), ('’s', 0.6514)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -2548,28 +2589,28 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that you</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How would you describe the feeling of touching velvet?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.2270916998386383</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9058996438980103</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>0.6466038227081299</v>
+        <v>-0</v>
       </c>
       <c r="H56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), (' you', 0.3486)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2586,28 +2627,28 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that’s</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How would you describe the feeling of touching velvet?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.424263209104538</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9444428682327271</v>
+        <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>0.5584724545478821</v>
+        <v>-0</v>
       </c>
       <c r="H57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), ('’s', 0.6514)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -2624,28 +2665,28 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? Soft, smooth, and luxurious, right? That’s the feeling you get</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How would you describe the feeling of touching velvet?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.1355009078979492</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>0.875244677066803</v>
+        <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>0.9097656011581421</v>
+        <v>-0</v>
       </c>
       <c r="H58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>[(' Soft', 0.3486), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), (',', 1.0), (' right', 1.0), ('?', 1.0), (' That', 0.5), ('’s', 1.0), (' the', 0.7773), (' feeling', 1.0), (' you', 1.0), (' get', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -2662,28 +2703,28 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? Soft, smooth, and luxurious, right? That’s the feeling you get</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How would you describe the feeling of touching velvet?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.1355009078979492</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>0.875244677066803</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>0.9097656011581421</v>
+        <v>-0</v>
       </c>
       <c r="H59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>[(' Soft', 0.3486), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), (',', 1.0), (' right', 1.0), ('?', 1.0), (' That', 0.5), ('’s', 1.0), (' the', 0.7773), (' feeling', 1.0), (' you', 1.0), (' get', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -2700,28 +2741,28 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? Soft, smooth, and luxurious, right? Now imagine that same feeling on</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How would you describe the feeling of touching velvet?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.1743225604295731</v>
+        <v>1</v>
       </c>
       <c r="F60" t="n">
-        <v>0.8900687694549561</v>
+        <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>0.713941216468811</v>
+        <v>-0</v>
       </c>
       <c r="H60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>[(' Soft', 0.3486), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), (',', 1.0), (' right', 1.0), ('?', 1.0), (' Now', 0.5), (' imagine', 1.0), (' that', 1.0), (' same', 1.0), (' feeling', 1.0), (' on', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -2738,28 +2779,28 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that’s</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How would you describe the feeling of touching velvet?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.424263209104538</v>
+        <v>1</v>
       </c>
       <c r="F61" t="n">
-        <v>0.9444428682327271</v>
+        <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>0.5584724545478821</v>
+        <v>-0</v>
       </c>
       <c r="H61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), ('’s', 0.6514)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -2776,7 +2817,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who was the first president of the United States?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -2789,15 +2830,15 @@
         <v>0.3673676252365112</v>
       </c>
       <c r="H62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>[(' George', 0.3486), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 0.3486), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -2814,28 +2855,28 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who was the first president of the United States?.://www.google.com/url?sa=t&amp;source=web&amp;</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.3486451208591461</v>
+        <v>0.09634663909673691</v>
       </c>
       <c r="F63" t="n">
-        <v>0.9321638345718384</v>
+        <v>0.8555704355239868</v>
       </c>
       <c r="G63" t="n">
-        <v>0.3673676252365112</v>
+        <v>1.205076336860657</v>
       </c>
       <c r="H63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>[(' George', 0.3486), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 0.6514), ('.com', 1.0), ('/url', 1.0), ('?', 0.6514), ('sa', 1.0), ('=t', 0.6514), ('&amp;', 1.0), ('source', 1.0), ('=', 1.0), ('web', 1.0), ('&amp;', 0.3486)]</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -2852,28 +2893,28 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? What was the first state admitted to the Union? What is the capital of</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who was the first president of the United States?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F64" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G64" t="n">
-        <v>0.279236227273941</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H64" t="b">
         <v>0</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>[(' What', 0.6514), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' state', 1.0), (' admitted', 1.0), (' to', 1.0), (' the', 1.0), (' Union', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' of', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 0.3486), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2890,28 +2931,28 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? What was the first state admitted to the Union? What is the capital of</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who was the first president of the United States?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F65" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G65" t="n">
-        <v>0.279236227273941</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H65" t="b">
         <v>0</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>[(' What', 0.6514), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' state', 1.0), (' admitted', 1.0), (' to', 1.0), (' the', 1.0), (' Union', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' of', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 0.3486), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2928,28 +2969,28 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? What was the first state admitted to the Union? What is the capital of</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who was the first president of the United States?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F66" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G66" t="n">
-        <v>0.279236227273941</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H66" t="b">
         <v>0</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>[(' What', 0.6514), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' state', 1.0), (' admitted', 1.0), (' to', 1.0), (' the', 1.0), (' Union', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' of', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 0.3486), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2966,28 +3007,28 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? What was the first state admitted to the Union? What is the capital of</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who was the first president of the United States?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F67" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G67" t="n">
-        <v>0.279236227273941</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H67" t="b">
         <v>0</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>[(' What', 0.6514), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' state', 1.0), (' admitted', 1.0), (' to', 1.0), (' the', 1.0), (' Union', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' of', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 0.3486), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -3004,28 +3045,28 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? What was the first state admitted to the Union? What is the capital of</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who was the first president of the United States?.://www.google.com/url?sa=t&amp;source=web&amp;</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.09634663909673691</v>
       </c>
       <c r="F68" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.8555704355239868</v>
       </c>
       <c r="G68" t="n">
-        <v>0.279236227273941</v>
+        <v>1.205076336860657</v>
       </c>
       <c r="H68" t="b">
         <v>0</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>[(' What', 0.6514), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' state', 1.0), (' admitted', 1.0), (' to', 1.0), (' the', 1.0), (' Union', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' of', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 0.6514), ('.com', 1.0), ('/url', 1.0), ('?', 0.6514), ('sa', 1.0), ('=t', 0.6514), ('&amp;', 1.0), ('source', 1.0), ('=', 1.0), ('web', 1.0), ('&amp;', 0.3486)]</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -3042,28 +3083,28 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? What was the first state admitted to the Union? What is the capital of</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who was the first president of the United States?.://www.google.com/url?sa=t&amp;source=web&amp;</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.09634663909673691</v>
       </c>
       <c r="F69" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.8555704355239868</v>
       </c>
       <c r="G69" t="n">
-        <v>0.279236227273941</v>
+        <v>1.205076336860657</v>
       </c>
       <c r="H69" t="b">
         <v>0</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>[(' What', 0.6514), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' state', 1.0), (' admitted', 1.0), (' to', 1.0), (' the', 1.0), (' Union', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' of', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 0.6514), ('.com', 1.0), ('/url', 1.0), ('?', 0.6514), ('sa', 1.0), ('=t', 0.6514), ('&amp;', 1.0), ('source', 1.0), ('=', 1.0), ('web', 1.0), ('&amp;', 0.3486)]</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -3080,28 +3121,28 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who was the first president of the United States?.://www.google.com/url?sa=t&amp;source=web&amp;r</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.3486451208591461</v>
+        <v>0.1799992620944977</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9321638345718384</v>
+        <v>0.8919723033905029</v>
       </c>
       <c r="G70" t="n">
-        <v>0.3673676252365112</v>
+        <v>1.116944909095764</v>
       </c>
       <c r="H70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>[(' George', 0.3486), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 0.6514), ('.com', 1.0), ('/url', 1.0), ('?', 0.6514), ('sa', 1.0), ('=t', 0.6514), ('&amp;', 1.0), ('source', 1.0), ('=', 1.0), ('web', 1.0), ('&amp;r', 0.6514)]</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -3118,28 +3159,28 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? What was the first state admitted to the Union? What is the capital of</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who was the first president of the United States?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F71" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G71" t="n">
-        <v>0.279236227273941</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H71" t="b">
         <v>0</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>[(' What', 0.6514), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' state', 1.0), (' admitted', 1.0), (' to', 1.0), (' the', 1.0), (' Union', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' of', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 0.3486), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -3156,29 +3197,28 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? Who is the author of 'Pride and Prejudice'?
-Who</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who is the author of 'Pride and Prejudice'?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.4829698204994202</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>0.9526382088661194</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>0.3515059649944305</v>
+        <v>-0</v>
       </c>
       <c r="H72" t="b">
         <v>0</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>[(' Who', 0.483), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Who', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -3195,29 +3235,28 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? Who is the author of 'Pride and Prejudice'?
-Who</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who is the author of 'Pride and Prejudice'?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.4829698204994202</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
-        <v>0.9526382088661194</v>
+        <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>0.3515059649944305</v>
+        <v>-0</v>
       </c>
       <c r="H73" t="b">
         <v>0</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>[(' Who', 0.483), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Who', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -3234,29 +3273,28 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? Who is the author of 'Pride and Prejudice'?
-Who</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who is the author of 'Pride and Prejudice'?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.4829698204994202</v>
+        <v>1</v>
       </c>
       <c r="F74" t="n">
-        <v>0.9526382088661194</v>
+        <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>0.3515059649944305</v>
+        <v>-0</v>
       </c>
       <c r="H74" t="b">
         <v>0</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>[(' Who', 0.483), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Who', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -3273,29 +3311,28 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? Who is the author of 'Pride and Prejudice'?
-Who</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who is the author of 'Pride and Prejudice'?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.4829698204994202</v>
+        <v>1</v>
       </c>
       <c r="F75" t="n">
-        <v>0.9526382088661194</v>
+        <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>0.3515059649944305</v>
+        <v>-0</v>
       </c>
       <c r="H75" t="b">
         <v>0</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>[(' Who', 0.483), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Who', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -3312,28 +3349,28 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? What is the name of the main character in 'Pride and Prejud</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who is the author of 'Pride and Prejudice'?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.2585151195526123</v>
+        <v>1</v>
       </c>
       <c r="F76" t="n">
-        <v>0.9137605428695679</v>
+        <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>0.3497195243835449</v>
+        <v>-0</v>
       </c>
       <c r="H76" t="b">
         <v>0</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>[(' What', 0.2585), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' character', 1.0), (' in', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -3350,29 +3387,28 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? Who is the author of 'Pride and Prejudice'?
-Who</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who is the author of 'Pride and Prejudice'?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.4829698204994202</v>
+        <v>1</v>
       </c>
       <c r="F77" t="n">
-        <v>0.9526382088661194</v>
+        <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0.3515059649944305</v>
+        <v>-0</v>
       </c>
       <c r="H77" t="b">
         <v>0</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>[(' Who', 0.483), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Who', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -3389,28 +3425,28 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? What is the name of the main character in 'Pride and Prejud</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who is the author of 'Pride and Prejudice'?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.2585151195526123</v>
+        <v>1</v>
       </c>
       <c r="F78" t="n">
-        <v>0.9137605428695679</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>0.3497195243835449</v>
+        <v>-0</v>
       </c>
       <c r="H78" t="b">
         <v>0</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>[(' What', 0.2585), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' character', 1.0), (' in', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -3427,29 +3463,28 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? Who is the author of 'Pride and Prejudice'?
-Who</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who is the author of 'Pride and Prejudice'?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.4829698204994202</v>
+        <v>1</v>
       </c>
       <c r="F79" t="n">
-        <v>0.9526382088661194</v>
+        <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>0.3515059649944305</v>
+        <v>-0</v>
       </c>
       <c r="H79" t="b">
         <v>0</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>[(' Who', 0.483), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Who', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -3466,29 +3501,28 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? Jane Austen
-What is the name of the main character in 'P</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who is the author of 'Pride and Prejudice'?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.2585151195526123</v>
+        <v>1</v>
       </c>
       <c r="F80" t="n">
-        <v>0.9137605428695679</v>
+        <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>0.3497195243835449</v>
+        <v>-0</v>
       </c>
       <c r="H80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>[(' Jane', 0.2585), (' Aust', 1.0), ('en', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' character', 1.0), (' in', 1.0), (" '", 1.0), ('P', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -3505,29 +3539,28 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? Who is the author of 'Pride and Prejudice'?
-Who</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who is the author of 'Pride and Prejudice'?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.4829698204994202</v>
+        <v>1</v>
       </c>
       <c r="F81" t="n">
-        <v>0.9526382088661194</v>
+        <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>0.3515059649944305</v>
+        <v>-0</v>
       </c>
       <c r="H81" t="b">
         <v>0</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>[(' Who', 0.483), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Who', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -3544,28 +3577,28 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci. What is the Mona Lisa? A portrait of Lisa G</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who painted the Mona Lisa?.://www.google.com/url?q=https://www.google.com/url?q</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.1113500744104385</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F82" t="n">
-        <v>0.8638653159141541</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G82" t="n">
-        <v>0.6810534000396729</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 0.2227), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('?', 1.0), (' A', 1.0), (' portrait', 0.5), (' of', 1.0), (' Lisa', 1.0), (' G', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?q', 0.3486), ('=https', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?q', 1.0)]</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -3582,28 +3615,28 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci, of course. But who painted the Mona Lisa’s smile</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who painted the Mona Lisa?.://www.google.com/url?sa=t&amp;source=web&amp;r</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.424263209104538</v>
       </c>
       <c r="F83" t="n">
-        <v>0.9833449721336365</v>
+        <v>0.9444428682327271</v>
       </c>
       <c r="G83" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.5584724545478821</v>
       </c>
       <c r="H83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (',', 0.7773), (' of', 1.0), (' course', 1.0), ('.', 1.0), (' But', 1.0), (' who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 0.6514), ('sa', 1.0), ('=t', 0.6514), ('&amp;', 1.0), ('source', 1.0), ('=', 1.0), ('web', 1.0), ('&amp;r', 1.0)]</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -3620,28 +3653,28 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci, of course. But who painted the Mona Lisa’s smile</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who painted the Mona Lisa?.://www.google.com/url?q=https://www.google.com/url?q</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F84" t="n">
-        <v>0.9833449721336365</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G84" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (',', 0.7773), (' of', 1.0), (' course', 1.0), ('.', 1.0), (' But', 1.0), (' who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?q', 0.3486), ('=https', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?q', 1.0)]</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -3658,28 +3691,28 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci. What is the Mona Lisa? A portrait of Lisa G</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who painted the Mona Lisa?.://www.google.com/url?q=https://www.google.com/url?q</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.1113500744104385</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F85" t="n">
-        <v>0.8638653159141541</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G85" t="n">
-        <v>0.6810534000396729</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 0.2227), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('?', 1.0), (' A', 1.0), (' portrait', 0.5), (' of', 1.0), (' Lisa', 1.0), (' G', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?q', 0.3486), ('=https', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?q', 1.0)]</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -3696,28 +3729,28 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci. What is the Mona Lisa? A painting. What is</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who painted the Mona Lisa?.://www.google.com/url?sa=U&amp;ved=0</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.1113500744104385</v>
+        <v>0.2270916998386383</v>
       </c>
       <c r="F86" t="n">
-        <v>0.8638653159141541</v>
+        <v>0.9058996438980103</v>
       </c>
       <c r="G86" t="n">
-        <v>0.6810534000396729</v>
+        <v>0.6466038227081299</v>
       </c>
       <c r="H86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 0.2227), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('?', 1.0), (' A', 1.0), (' painting', 0.5), ('.', 1.0), (' What', 1.0), (' is', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 0.6514), ('sa', 1.0), ('=', 0.3486), ('U', 1.0), ('&amp;', 1.0), ('ved', 1.0), ('=', 1.0), ('0', 1.0)]</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -3734,28 +3767,28 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci, of course. But who painted the Mona Lisa’s smile</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who painted the Mona Lisa?.://www.google.com/url?sa=U&amp;ved=0</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.2270916998386383</v>
       </c>
       <c r="F87" t="n">
-        <v>0.9833449721336365</v>
+        <v>0.9058996438980103</v>
       </c>
       <c r="G87" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.6466038227081299</v>
       </c>
       <c r="H87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (',', 0.7773), (' of', 1.0), (' course', 1.0), ('.', 1.0), (' But', 1.0), (' who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 0.6514), ('sa', 1.0), ('=', 0.3486), ('U', 1.0), ('&amp;', 1.0), ('ved', 1.0), ('=', 1.0), ('0', 1.0)]</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -3772,28 +3805,28 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci, of course. But who painted the Mona Lisa’s smile</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who painted the Mona Lisa?.://www.google.com/url?sa=t&amp;source=web&amp;r</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.424263209104538</v>
       </c>
       <c r="F88" t="n">
-        <v>0.9833449721336365</v>
+        <v>0.9444428682327271</v>
       </c>
       <c r="G88" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.5584724545478821</v>
       </c>
       <c r="H88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (',', 0.7773), (' of', 1.0), (' course', 1.0), ('.', 1.0), (' But', 1.0), (' who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 0.6514), ('sa', 1.0), ('=t', 0.6514), ('&amp;', 1.0), ('source', 1.0), ('=', 1.0), ('web', 1.0), ('&amp;r', 1.0)]</t>
         </is>
       </c>
       <c r="J88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -3810,28 +3843,28 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci, of course. But who painted the Mona Lisa’s smile</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who painted the Mona Lisa?.://www.google.com/url?q=https://www.google.com/url?q</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F89" t="n">
-        <v>0.9833449721336365</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G89" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (',', 0.7773), (' of', 1.0), (' course', 1.0), ('.', 1.0), (' But', 1.0), (' who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?q', 0.3486), ('=https', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?q', 1.0)]</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -3848,28 +3881,28 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci. What is the Mona Lisa? A portrait of Lisa G</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who painted the Mona Lisa?.://www.google.com/url?q=https://www.google.com/url?q</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.1113500744104385</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F90" t="n">
-        <v>0.8638653159141541</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G90" t="n">
-        <v>0.6810534000396729</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 0.2227), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('?', 1.0), (' A', 1.0), (' portrait', 0.5), (' of', 1.0), (' Lisa', 1.0), (' G', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?q', 0.3486), ('=https', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?q', 1.0)]</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -3886,28 +3919,28 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci. What is the Mona Lisa? A portrait of Lisa G</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Who painted the Mona Lisa?.://www.google.com/url?sa=t&amp;source=web&amp;r</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.1113500744104385</v>
+        <v>0.424263209104538</v>
       </c>
       <c r="F91" t="n">
-        <v>0.8638653159141541</v>
+        <v>0.9444428682327271</v>
       </c>
       <c r="G91" t="n">
-        <v>0.6810534000396729</v>
+        <v>0.5584724545478821</v>
       </c>
       <c r="H91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 0.2227), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('?', 1.0), (' A', 1.0), (' portrait', 0.5), (' of', 1.0), (' Lisa', 1.0), (' G', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 0.6514), ('sa', 1.0), ('=t', 0.6514), ('&amp;', 1.0), ('source', 1.0), ('=', 1.0), ('web', 1.0), ('&amp;r', 1.0)]</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -3924,24 +3957,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is your favorite color?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.8670357465744019</v>
       </c>
       <c r="F92" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.9905334115028381</v>
       </c>
       <c r="G92" t="n">
-        <v>0.279236227273941</v>
+        <v>0.1237043887376785</v>
       </c>
       <c r="H92" t="b">
         <v>0</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.867), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J92" t="n">
@@ -3962,24 +3996,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is your favorite color?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.8670357465744019</v>
       </c>
       <c r="F93" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.9905334115028381</v>
       </c>
       <c r="G93" t="n">
-        <v>0.279236227273941</v>
+        <v>0.1237043887376785</v>
       </c>
       <c r="H93" t="b">
         <v>0</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.867), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J93" t="n">
@@ -4000,24 +4035,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is your favorite color?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.8670357465744019</v>
       </c>
       <c r="F94" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.9905334115028381</v>
       </c>
       <c r="G94" t="n">
-        <v>0.279236227273941</v>
+        <v>0.1237043887376785</v>
       </c>
       <c r="H94" t="b">
         <v>0</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.867), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J94" t="n">
@@ -4038,24 +4074,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is your favorite color?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.8670357465744019</v>
       </c>
       <c r="F95" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.9905334115028381</v>
       </c>
       <c r="G95" t="n">
-        <v>0.279236227273941</v>
+        <v>0.1237043887376785</v>
       </c>
       <c r="H95" t="b">
         <v>0</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.867), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J95" t="n">
@@ -4076,24 +4113,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is your favorite color?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.8670357465744019</v>
       </c>
       <c r="F96" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.9905334115028381</v>
       </c>
       <c r="G96" t="n">
-        <v>0.279236227273941</v>
+        <v>0.1237043887376785</v>
       </c>
       <c r="H96" t="b">
         <v>0</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.867), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J96" t="n">
@@ -4114,24 +4152,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is your favorite color?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.8670357465744019</v>
       </c>
       <c r="F97" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.9905334115028381</v>
       </c>
       <c r="G97" t="n">
-        <v>0.279236227273941</v>
+        <v>0.1237043887376785</v>
       </c>
       <c r="H97" t="b">
         <v>0</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.867), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J97" t="n">
@@ -4152,24 +4191,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is your favorite color?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.8670357465744019</v>
       </c>
       <c r="F98" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.9905334115028381</v>
       </c>
       <c r="G98" t="n">
-        <v>0.279236227273941</v>
+        <v>0.1237043887376785</v>
       </c>
       <c r="H98" t="b">
         <v>0</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.867), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J98" t="n">
@@ -4190,24 +4230,24 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is your favorite color?.://www.google.com/url?sa=U&amp;ved=0</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.02820591069757938</v>
       </c>
       <c r="F99" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.7882960438728333</v>
       </c>
       <c r="G99" t="n">
-        <v>0.279236227273941</v>
+        <v>1.173324584960938</v>
       </c>
       <c r="H99" t="b">
         <v>0</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 0.133), ('.google', 0.6514), ('.com', 1.0), ('/url', 0.5), ('?', 1.0), ('sa', 1.0), ('=', 0.6514), ('U', 1.0), ('&amp;', 1.0), ('ved', 1.0), ('=', 1.0), ('0', 1.0)]</t>
         </is>
       </c>
       <c r="J99" t="n">
@@ -4228,24 +4268,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is your favorite color?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.8670357465744019</v>
       </c>
       <c r="F100" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.9905334115028381</v>
       </c>
       <c r="G100" t="n">
-        <v>0.279236227273941</v>
+        <v>0.1237043887376785</v>
       </c>
       <c r="H100" t="b">
         <v>0</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.867), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J100" t="n">
@@ -4266,24 +4307,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is your favorite color?.://en.wikipedia.org/wiki/Paris
+Given these facts:</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.8670357465744019</v>
       </c>
       <c r="F101" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.9905334115028381</v>
       </c>
       <c r="G101" t="n">
-        <v>0.279236227273941</v>
+        <v>0.1237043887376785</v>
       </c>
       <c r="H101" t="b">
         <v>0</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.867), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J101" t="n">
@@ -4304,24 +4346,24 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What do you think of the meaning of life? What do you think of</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What do you think of the meaning of life?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F102" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H102" t="b">
         <v>0</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' do', 0.5), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J102" t="n">
@@ -4342,24 +4384,24 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What do you think of the meaning of life? What do you think of</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What do you think of the meaning of life?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F103" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="G103" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H103" t="b">
         <v>0</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' do', 0.5), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J103" t="n">
@@ -4380,24 +4422,24 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What do you think of the meaning of life? What do you think of</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What do you think of the meaning of life?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F104" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H104" t="b">
         <v>0</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' do', 0.5), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J104" t="n">
@@ -4418,24 +4460,24 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What is the meaning of life? What is the meaning of life? What</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What do you think of the meaning of life?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F105" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H105" t="b">
         <v>0</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 0.5), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J105" t="n">
@@ -4456,24 +4498,24 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What is the meaning of life? What is the meaning of life? What</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What do you think of the meaning of life?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F106" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="G106" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H106" t="b">
         <v>0</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 0.5), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J106" t="n">
@@ -4494,24 +4536,24 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What is the meaning of life? What is the meaning of life? What</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What do you think of the meaning of life?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F107" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="G107" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H107" t="b">
         <v>0</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 0.5), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J107" t="n">
@@ -4532,24 +4574,24 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What is the meaning of life? What is the meaning of life? What</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What do you think of the meaning of life?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F108" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H108" t="b">
         <v>0</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 0.5), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J108" t="n">
@@ -4570,24 +4612,24 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What do you think of the meaning of life? What do you think of</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What do you think of the meaning of life?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F109" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="G109" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H109" t="b">
         <v>0</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' do', 0.5), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J109" t="n">
@@ -4608,24 +4650,24 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What do you think of the meaning of life? What do you think of</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What do you think of the meaning of life?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F110" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H110" t="b">
         <v>0</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' do', 0.5), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J110" t="n">
@@ -4646,24 +4688,24 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What is the meaning of life? What is the meaning of life? What</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What do you think of the meaning of life?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F111" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H111" t="b">
         <v>0</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 0.5), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J111" t="n">
@@ -4684,24 +4726,24 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What comes after the end?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G112" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H112" t="b">
         <v>0</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 0.5), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J112" t="n">
@@ -4722,24 +4764,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What comes after the end?.://www.://www. is the answer.
+Given</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G113" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H113" t="b">
         <v>0</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), (' is', 0.5), (' the', 1.0), (' answer', 1.0), ('.\n', 1.0), ('Given', 1.0)]</t>
         </is>
       </c>
       <c r="J113" t="n">
@@ -4760,24 +4803,24 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What comes after the end?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F114" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G114" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H114" t="b">
         <v>0</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 0.5), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J114" t="n">
@@ -4798,24 +4841,24 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What comes after the end?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F115" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G115" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H115" t="b">
         <v>0</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 0.5), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J115" t="n">
@@ -4836,24 +4879,24 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What comes after the end?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G116" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H116" t="b">
         <v>0</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 0.5), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J116" t="n">
@@ -4874,24 +4917,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What comes after the end?.://www.://www. is the answer.
+Given</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F117" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G117" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H117" t="b">
         <v>0</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), (' is', 0.5), (' the', 1.0), (' answer', 1.0), ('.\n', 1.0), ('Given', 1.0)]</t>
         </is>
       </c>
       <c r="J117" t="n">
@@ -4912,24 +4956,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What comes after the end?.://www.://www. is the answer.
+Given</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F118" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G118" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H118" t="b">
         <v>0</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), (' is', 0.5), (' the', 1.0), (' answer', 1.0), ('.\n', 1.0), ('Given', 1.0)]</t>
         </is>
       </c>
       <c r="J118" t="n">
@@ -4950,24 +4995,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What comes after the end?.://www.://www. is the answer.
+Given</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G119" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H119" t="b">
         <v>0</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), (' is', 0.5), (' the', 1.0), (' answer', 1.0), ('.\n', 1.0), ('Given', 1.0)]</t>
         </is>
       </c>
       <c r="J119" t="n">
@@ -4988,24 +5034,24 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What comes after the end?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F120" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G120" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H120" t="b">
         <v>0</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 0.5), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -5026,24 +5072,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What comes after the end?.://www.://www. is the answer.
+Given</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F121" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G121" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H121" t="b">
         <v>0</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), (' is', 0.5), (' the', 1.0), (' answer', 1.0), ('.\n', 1.0), ('Given', 1.0)]</t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -5064,28 +5111,28 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven: Africa, Antarctica, Asia, Australia/Oceania</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How many continents are there on Earth?.://www.google.com/ is the answer.://www</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.2227001488208771</v>
+        <v>0.1628387123346329</v>
       </c>
       <c r="F122" t="n">
-        <v>0.9047210812568665</v>
+        <v>0.8860342502593994</v>
       </c>
       <c r="G122" t="n">
-        <v>0.334479808807373</v>
+        <v>0.9723833799362183</v>
       </c>
       <c r="H122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), (':', 0.2227), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), ('/O', 1.0), ('ce', 1.0), ('ania', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 0.5), ('.com', 1.0), ('/', 0.6514), (' is', 1.0), (' the', 1.0), (' answer', 1.0), ('.', 0.5), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0)]</t>
         </is>
       </c>
       <c r="J122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -5102,28 +5149,28 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The continents are Africa, Antarctica, Asia, Australia</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How many continents are there on Earth?.://www.google.com/url?sa=U&amp;ved=0</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.0607767142355442</v>
       </c>
       <c r="F123" t="n">
-        <v>0.9389386773109436</v>
+        <v>0.8296899199485779</v>
       </c>
       <c r="G123" t="n">
-        <v>0.5423979759216309</v>
+        <v>1.081308841705322</v>
       </c>
       <c r="H123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' continents', 0.5), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 0.5), ('.com', 1.0), ('/url', 0.3486), ('?', 1.0), ('sa', 1.0), ('=', 0.3486), ('U', 1.0), ('&amp;', 1.0), ('ved', 1.0), ('=', 1.0), ('0', 1.0)]</t>
         </is>
       </c>
       <c r="J123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -5140,28 +5187,29 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The seven continents are Africa, Antarctica, Asia,</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How many continents are there on Earth?.://www.google.com/ is the answer.
+Given these facts:</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.1628387123346329</v>
       </c>
       <c r="F124" t="n">
-        <v>0.9389386773109436</v>
+        <v>0.8860342502593994</v>
       </c>
       <c r="G124" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.9723833799362183</v>
       </c>
       <c r="H124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' seven', 0.5), (' continents', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 0.5), ('.com', 1.0), ('/', 0.6514), (' is', 1.0), (' the', 1.0), (' answer', 1.0), ('.\n', 0.5), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0)]</t>
         </is>
       </c>
       <c r="J124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -5178,28 +5226,28 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The seven continents are Africa, Antarctica, Asia,</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How many continents are there on Earth?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.5</v>
       </c>
       <c r="F125" t="n">
-        <v>0.9389386773109436</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G125" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' seven', 0.5), (' continents', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 0.5), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -5216,28 +5264,28 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The seven continents are Africa, Antarctica, Asia,</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How many continents are there on Earth?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.5</v>
       </c>
       <c r="F126" t="n">
-        <v>0.9389386773109436</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G126" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' seven', 0.5), (' continents', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 0.5), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -5254,28 +5302,28 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The continents are Africa, Antarctica, Asia, Australia</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How many continents are there on Earth?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.5</v>
       </c>
       <c r="F127" t="n">
-        <v>0.9389386773109436</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G127" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' continents', 0.5), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 0.5), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -5292,28 +5340,28 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The seven continents are Africa, Antarctica, Asia,</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How many continents are there on Earth?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.5</v>
       </c>
       <c r="F128" t="n">
-        <v>0.9389386773109436</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G128" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' seven', 0.5), (' continents', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 0.5), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -5330,28 +5378,29 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The seven continents are Africa, Antarctica, Asia,</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How many continents are there on Earth?.://www.google.com/ is the answer.
+Given these facts:</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.1628387123346329</v>
       </c>
       <c r="F129" t="n">
-        <v>0.9389386773109436</v>
+        <v>0.8860342502593994</v>
       </c>
       <c r="G129" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.9723833799362183</v>
       </c>
       <c r="H129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' seven', 0.5), (' continents', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 0.5), ('.com', 1.0), ('/', 0.6514), (' is', 1.0), (' the', 1.0), (' answer', 1.0), ('.\n', 0.5), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0)]</t>
         </is>
       </c>
       <c r="J129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -5368,28 +5417,28 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven: Africa, Antarctica, Asia, Australia/Oceania</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How many continents are there on Earth?.://www.google.com/url?sa=t&amp;source=web&amp;r</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.2227001488208771</v>
+        <v>0.1135458499193192</v>
       </c>
       <c r="F130" t="n">
-        <v>0.9047210812568665</v>
+        <v>0.8649906516075134</v>
       </c>
       <c r="G130" t="n">
-        <v>0.334479808807373</v>
+        <v>0.9931774139404297</v>
       </c>
       <c r="H130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), (':', 0.2227), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), ('/O', 1.0), ('ce', 1.0), ('ania', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 0.5), ('.com', 1.0), ('/url', 0.3486), ('?', 1.0), ('sa', 1.0), ('=t', 0.6514), ('&amp;', 1.0), ('source', 1.0), ('=', 1.0), ('web', 1.0), ('&amp;r', 1.0)]</t>
         </is>
       </c>
       <c r="J130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -5406,28 +5455,29 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The seven continents are Africa, Antarctica, Asia,</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How many continents are there on Earth?.://www.google.com/ is the answer.
+Given these facts:</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.1628387123346329</v>
       </c>
       <c r="F131" t="n">
-        <v>0.9389386773109436</v>
+        <v>0.8860342502593994</v>
       </c>
       <c r="G131" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.9723833799362183</v>
       </c>
       <c r="H131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' seven', 0.5), (' continents', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 0.5), ('.com', 1.0), ('/', 0.6514), (' is', 1.0), (' the', 1.0), (' answer', 1.0), ('.\n', 0.5), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0)]</t>
         </is>
       </c>
       <c r="J131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -5444,28 +5494,28 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. The boiling point of</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the boiling point of water in Celsius?.://www.google.com/ 1. 100 2.</t>
         </is>
       </c>
       <c r="E132" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.9117224812507629</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.6931471824645996</v>
+      </c>
+      <c r="H132" t="b">
+        <v>1</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 0.5), ('.google', 1.0), ('.com', 1.0), ('/', 1.0), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('100', 1.0), (' ', 0.5), ('2', 1.0), ('.', 1.0)]</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
         <v>0.5</v>
-      </c>
-      <c r="F132" t="n">
-        <v>0.9548416137695312</v>
-      </c>
-      <c r="G132" t="n">
-        <v>0.3465735912322998</v>
-      </c>
-      <c r="H132" t="b">
-        <v>1</v>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 0.5), (' boiling', 1.0), (' point', 1.0), (' of', 1.0)]</t>
-        </is>
-      </c>
-      <c r="J132" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -5482,28 +5532,29 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. This is the temperature</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the boiling point of water in Celsius?.://en.wikipedia.org/wiki/Boiling_point
+Given these facts</t>
         </is>
       </c>
       <c r="E133" t="n">
+        <v>0.1743225604295731</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.8900687694549561</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.713941216468811</v>
+      </c>
+      <c r="H133" t="b">
+        <v>0</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.5), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Bo', 0.3486), ('iling', 1.0), ('_point', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0)]</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
         <v>0.5</v>
-      </c>
-      <c r="F133" t="n">
-        <v>0.9548416137695312</v>
-      </c>
-      <c r="G133" t="n">
-        <v>0.3465735912322998</v>
-      </c>
-      <c r="H133" t="b">
-        <v>1</v>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0)]</t>
-        </is>
-      </c>
-      <c r="J133" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -5520,28 +5571,28 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. This is the temperature</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the boiling point of water in Celsius?.://en.wikipedia.org/wiki/Paris, Paris.ondon, London</t>
         </is>
       </c>
       <c r="E134" t="n">
+        <v>0.05677292495965958</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.8259290456771851</v>
+      </c>
+      <c r="G134" t="n">
+        <v>1.339751005172729</v>
+      </c>
+      <c r="H134" t="b">
+        <v>0</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.5), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 0.6514), (',', 0.5), (' Paris', 1.0), ('.', 1.0), ('ondon', 0.3486), (',', 1.0), (' London', 1.0)]</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
         <v>0.5</v>
-      </c>
-      <c r="F134" t="n">
-        <v>0.9548416137695312</v>
-      </c>
-      <c r="G134" t="n">
-        <v>0.3465735912322998</v>
-      </c>
-      <c r="H134" t="b">
-        <v>1</v>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0)]</t>
-        </is>
-      </c>
-      <c r="J134" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -5558,28 +5609,28 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. This is the temperature</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the boiling point of water in Celsius?.://www.google.com/ 1. 100 2.</t>
         </is>
       </c>
       <c r="E135" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.9117224812507629</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.6931471824645996</v>
+      </c>
+      <c r="H135" t="b">
+        <v>1</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 0.5), ('.google', 1.0), ('.com', 1.0), ('/', 1.0), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('100', 1.0), (' ', 0.5), ('2', 1.0), ('.', 1.0)]</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
         <v>0.5</v>
-      </c>
-      <c r="F135" t="n">
-        <v>0.9548416137695312</v>
-      </c>
-      <c r="G135" t="n">
-        <v>0.3465735912322998</v>
-      </c>
-      <c r="H135" t="b">
-        <v>1</v>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0)]</t>
-        </is>
-      </c>
-      <c r="J135" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -5596,28 +5647,28 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. This is the temperature</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the boiling point of water in Celsius?.://en.wikipedia.org/wiki/Paris, Paris. 2.</t>
         </is>
       </c>
       <c r="E136" t="n">
+        <v>0.1060657873749733</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.8610697984695435</v>
+      </c>
+      <c r="G136" t="n">
+        <v>1.251619577407837</v>
+      </c>
+      <c r="H136" t="b">
+        <v>0</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.5), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 0.6514), (',', 0.5), (' Paris', 1.0), ('.', 1.0), (' ', 0.6514), ('2', 1.0), ('.', 1.0)]</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
         <v>0.5</v>
-      </c>
-      <c r="F136" t="n">
-        <v>0.9548416137695312</v>
-      </c>
-      <c r="G136" t="n">
-        <v>0.3465735912322998</v>
-      </c>
-      <c r="H136" t="b">
-        <v>1</v>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0)]</t>
-        </is>
-      </c>
-      <c r="J136" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -5634,28 +5685,28 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. This is the temperature</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the boiling point of water in Celsius?.://www.google.com/ 1. 100 C 2</t>
         </is>
       </c>
       <c r="E137" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.9117224812507629</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.6931471824645996</v>
+      </c>
+      <c r="H137" t="b">
+        <v>1</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 0.5), ('.google', 1.0), ('.com', 1.0), ('/', 1.0), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('100', 1.0), (' C', 0.5), (' ', 1.0), ('2', 1.0)]</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
         <v>0.5</v>
-      </c>
-      <c r="F137" t="n">
-        <v>0.9548416137695312</v>
-      </c>
-      <c r="G137" t="n">
-        <v>0.3465735912322998</v>
-      </c>
-      <c r="H137" t="b">
-        <v>1</v>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0)]</t>
-        </is>
-      </c>
-      <c r="J137" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -5672,28 +5723,28 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. This is the temperature</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the boiling point of water in Celsius?.://www.google.com/ 1. 100 2.</t>
         </is>
       </c>
       <c r="E138" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.9117224812507629</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.6931471824645996</v>
+      </c>
+      <c r="H138" t="b">
+        <v>1</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 0.5), ('.google', 1.0), ('.com', 1.0), ('/', 1.0), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('100', 1.0), (' ', 0.5), ('2', 1.0), ('.', 1.0)]</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
         <v>0.5</v>
-      </c>
-      <c r="F138" t="n">
-        <v>0.9548416137695312</v>
-      </c>
-      <c r="G138" t="n">
-        <v>0.3465735912322998</v>
-      </c>
-      <c r="H138" t="b">
-        <v>1</v>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0)]</t>
-        </is>
-      </c>
-      <c r="J138" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="139">
@@ -5710,28 +5761,28 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. This is the temperature</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the boiling point of water in Celsius?.://www.google.com/ 1. 100 C 2</t>
         </is>
       </c>
       <c r="E139" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.9117224812507629</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.6931471824645996</v>
+      </c>
+      <c r="H139" t="b">
+        <v>1</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 0.5), ('.google', 1.0), ('.com', 1.0), ('/', 1.0), (' ', 1.0), ('1', 1.0), ('.', 1.0), (' ', 1.0), ('100', 1.0), (' C', 0.5), (' ', 1.0), ('2', 1.0)]</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
         <v>0.5</v>
-      </c>
-      <c r="F139" t="n">
-        <v>0.9548416137695312</v>
-      </c>
-      <c r="G139" t="n">
-        <v>0.3465735912322998</v>
-      </c>
-      <c r="H139" t="b">
-        <v>1</v>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0)]</t>
-        </is>
-      </c>
-      <c r="J139" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="140">
@@ -5748,28 +5799,28 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. This is the temperature</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the boiling point of water in Celsius?.://en.wikipedia.org/wiki/Paris, Paris.ondon, London</t>
         </is>
       </c>
       <c r="E140" t="n">
+        <v>0.05677292495965958</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.8259290456771851</v>
+      </c>
+      <c r="G140" t="n">
+        <v>1.339751005172729</v>
+      </c>
+      <c r="H140" t="b">
+        <v>0</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.5), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 0.6514), (',', 0.5), (' Paris', 1.0), ('.', 1.0), ('ondon', 0.3486), (',', 1.0), (' London', 1.0)]</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
         <v>0.5</v>
-      </c>
-      <c r="F140" t="n">
-        <v>0.9548416137695312</v>
-      </c>
-      <c r="G140" t="n">
-        <v>0.3465735912322998</v>
-      </c>
-      <c r="H140" t="b">
-        <v>1</v>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0)]</t>
-        </is>
-      </c>
-      <c r="J140" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -5786,28 +5837,28 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. This is the temperature</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the boiling point of water in Celsius?.://en.wikipedia.org/wiki/Paris, Paris. 2.</t>
         </is>
       </c>
       <c r="E141" t="n">
+        <v>0.1060657873749733</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.8610697984695435</v>
+      </c>
+      <c r="G141" t="n">
+        <v>1.251619577407837</v>
+      </c>
+      <c r="H141" t="b">
+        <v>0</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.5), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Paris', 0.6514), (',', 0.5), (' Paris', 1.0), ('.', 1.0), (' ', 0.6514), ('2', 1.0), ('.', 1.0)]</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
         <v>0.5</v>
-      </c>
-      <c r="F141" t="n">
-        <v>0.9548416137695312</v>
-      </c>
-      <c r="G141" t="n">
-        <v>0.3465735912322998</v>
-      </c>
-      <c r="H141" t="b">
-        <v>1</v>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0)]</t>
-        </is>
-      </c>
-      <c r="J141" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="142">
@@ -5824,28 +5875,28 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120?</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How many hours are there in a day?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F142" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G142" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 0.6514), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -5862,28 +5913,28 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120?</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How many hours are there in a day?.://www.google.com/url?q=https://www.google.com/url?q</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1</v>
+        <v>0.08716128021478653</v>
       </c>
       <c r="F143" t="n">
-        <v>1</v>
+        <v>0.8498746752738953</v>
       </c>
       <c r="G143" t="n">
-        <v>-0</v>
+        <v>1.060514807701111</v>
       </c>
       <c r="H143" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 0.3486), ('.com', 1.0), ('/url', 0.5), ('?q', 0.5), ('=https', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?q', 1.0)]</t>
         </is>
       </c>
       <c r="J143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -5900,28 +5951,28 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120?</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How many hours are there in a day?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F144" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G144" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 0.6514), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -5938,28 +5989,28 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120?</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How many hours are there in a day?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F145" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G145" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H145" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 0.6514), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -5976,28 +6027,28 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120?</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How many hours are there in a day?.://www.google.com/ is the answer to the question.</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1</v>
+        <v>0.05810752138495445</v>
       </c>
       <c r="F146" t="n">
-        <v>1</v>
+        <v>0.82720947265625</v>
       </c>
       <c r="G146" t="n">
-        <v>-0</v>
+        <v>1.080145359039307</v>
       </c>
       <c r="H146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 0.3486), ('.com', 1.0), ('/', 0.5), (' is', 1.0), (' the', 1.0), (' answer', 1.0), (' to', 0.3333), (' the', 1.0), (' question', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0)]</t>
         </is>
       </c>
       <c r="J146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -6014,28 +6065,28 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120?</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How many hours are there in a day?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G147" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 0.6514), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -6052,28 +6103,28 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120?</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How many hours are there in a day?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G148" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H148" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 0.6514), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -6090,28 +6141,28 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120?</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How many hours are there in a day?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G149" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 0.6514), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -6128,28 +6179,28 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120?</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How many hours are there in a day?.://www.google.com/ is the answer to the question.</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1</v>
+        <v>0.05810752138495445</v>
       </c>
       <c r="F150" t="n">
-        <v>1</v>
+        <v>0.82720947265625</v>
       </c>
       <c r="G150" t="n">
-        <v>-0</v>
+        <v>1.080145359039307</v>
       </c>
       <c r="H150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 0.3486), ('.com', 1.0), ('/', 0.5), (' is', 1.0), (' the', 1.0), (' answer', 1.0), (' to', 0.3333), (' the', 1.0), (' question', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0)]</t>
         </is>
       </c>
       <c r="J150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -6166,28 +6217,28 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120?</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: How many hours are there in a day?.://www.://www.://www.</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G151" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H151" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 0.6514), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -6204,28 +6255,28 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What language is primarily spoken in Brazil?.://www.google.com/url?sa=U&amp;ved=0</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F152" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G152" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H152" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 1.0), ('sa', 1.0), ('=', 0.6514), ('U', 1.0), ('&amp;', 1.0), ('ved', 1.0), ('=', 1.0), ('0', 1.0)]</t>
         </is>
       </c>
       <c r="J152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -6242,28 +6293,28 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What language is primarily spoken in Brazil?.://www.google.com/url?sa=t&amp;source=web&amp;</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1</v>
+        <v>0.2270916998386383</v>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
+        <v>0.9058996438980103</v>
       </c>
       <c r="G153" t="n">
-        <v>-0</v>
+        <v>0.6466038227081299</v>
       </c>
       <c r="H153" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 1.0), ('sa', 1.0), ('=t', 0.3486), ('&amp;', 1.0), ('source', 1.0), ('=', 1.0), ('web', 1.0), ('&amp;', 0.6514)]</t>
         </is>
       </c>
       <c r="J153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -6280,28 +6331,28 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What language is primarily spoken in Brazil?.://www.google.com/url?sa=t&amp;source=web&amp;r</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1</v>
+        <v>0.1215534284710884</v>
       </c>
       <c r="F154" t="n">
-        <v>1</v>
+        <v>0.868929386138916</v>
       </c>
       <c r="G154" t="n">
-        <v>-0</v>
+        <v>0.7347352504730225</v>
       </c>
       <c r="H154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 1.0), ('sa', 1.0), ('=t', 0.3486), ('&amp;', 1.0), ('source', 1.0), ('=', 1.0), ('web', 1.0), ('&amp;r', 0.3486)]</t>
         </is>
       </c>
       <c r="J154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -6318,28 +6369,28 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What language is primarily spoken in Brazil?.://www.google.com/url?sa=U&amp;ved=0</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F155" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G155" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 1.0), ('sa', 1.0), ('=', 0.6514), ('U', 1.0), ('&amp;', 1.0), ('ved', 1.0), ('=', 1.0), ('0', 1.0)]</t>
         </is>
       </c>
       <c r="J155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -6356,28 +6407,28 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What language is primarily spoken in Brazil?.://www.google.com/url?sa=U&amp;ved=0</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F156" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G156" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H156" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 1.0), ('sa', 1.0), ('=', 0.6514), ('U', 1.0), ('&amp;', 1.0), ('ved', 1.0), ('=', 1.0), ('0', 1.0)]</t>
         </is>
       </c>
       <c r="J156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -6394,28 +6445,28 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What language is primarily spoken in Brazil?.://www.google.com/url?sa=t&amp;source=web&amp;</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1</v>
+        <v>0.2270916998386383</v>
       </c>
       <c r="F157" t="n">
-        <v>1</v>
+        <v>0.9058996438980103</v>
       </c>
       <c r="G157" t="n">
-        <v>-0</v>
+        <v>0.6466038227081299</v>
       </c>
       <c r="H157" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 1.0), ('sa', 1.0), ('=t', 0.3486), ('&amp;', 1.0), ('source', 1.0), ('=', 1.0), ('web', 1.0), ('&amp;', 0.6514)]</t>
         </is>
       </c>
       <c r="J157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -6432,28 +6483,28 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What language is primarily spoken in Brazil?.://www.google.com/url?sa=U&amp;ved=0</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F158" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G158" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 1.0), ('sa', 1.0), ('=', 0.6514), ('U', 1.0), ('&amp;', 1.0), ('ved', 1.0), ('=', 1.0), ('0', 1.0)]</t>
         </is>
       </c>
       <c r="J158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -6470,28 +6521,28 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What language is primarily spoken in Brazil?.://www.google.com/url?sa=t&amp;source=web&amp;r</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1</v>
+        <v>0.1215534284710884</v>
       </c>
       <c r="F159" t="n">
-        <v>1</v>
+        <v>0.868929386138916</v>
       </c>
       <c r="G159" t="n">
-        <v>-0</v>
+        <v>0.7347352504730225</v>
       </c>
       <c r="H159" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 1.0), ('sa', 1.0), ('=t', 0.3486), ('&amp;', 1.0), ('source', 1.0), ('=', 1.0), ('web', 1.0), ('&amp;r', 0.3486)]</t>
         </is>
       </c>
       <c r="J159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -6508,28 +6559,28 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What language is primarily spoken in Brazil?.://www.google.com/url?sa=t&amp;source=web&amp;</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1</v>
+        <v>0.2270916998386383</v>
       </c>
       <c r="F160" t="n">
-        <v>1</v>
+        <v>0.9058996438980103</v>
       </c>
       <c r="G160" t="n">
-        <v>-0</v>
+        <v>0.6466038227081299</v>
       </c>
       <c r="H160" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 1.0), ('sa', 1.0), ('=t', 0.3486), ('&amp;', 1.0), ('source', 1.0), ('=', 1.0), ('web', 1.0), ('&amp;', 0.6514)]</t>
         </is>
       </c>
       <c r="J160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -6546,28 +6597,28 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What language is primarily spoken in Brazil?.://www.google.com/url?sa=U&amp;ved=0</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F161" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G161" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H161" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 1.0), ('sa', 1.0), ('=', 0.6514), ('U', 1.0), ('&amp;', 1.0), ('ved', 1.0), ('=', 1.0), ('0', 1.0)]</t>
         </is>
       </c>
       <c r="J161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -6584,24 +6635,24 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95%</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which language is spoken in Germany?.://www.google.com/url?sa=U&amp;ved=0</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F162" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G162" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H162" t="b">
         <v>1</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 1.0), ('sa', 1.0), ('=', 0.3486), ('U', 1.0), ('&amp;', 1.0), ('ved', 1.0), ('=', 1.0), ('0', 1.0)]</t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -6622,24 +6673,24 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95%</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which language is spoken in Germany?.://www.google.com/url?sa=U&amp;ved=0</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F163" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G163" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H163" t="b">
         <v>1</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 1.0), ('sa', 1.0), ('=', 0.3486), ('U', 1.0), ('&amp;', 1.0), ('ved', 1.0), ('=', 1.0), ('0', 1.0)]</t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -6660,24 +6711,24 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95%</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which language is spoken in Germany?.://www.google.com/url?sa=t&amp;source=web&amp;</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1</v>
+        <v>0.2270916998386383</v>
       </c>
       <c r="F164" t="n">
-        <v>1</v>
+        <v>0.9058996438980103</v>
       </c>
       <c r="G164" t="n">
-        <v>-0</v>
+        <v>0.6466038227081299</v>
       </c>
       <c r="H164" t="b">
         <v>1</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 1.0), ('sa', 1.0), ('=t', 0.6514), ('&amp;', 1.0), ('source', 1.0), ('=', 1.0), ('web', 1.0), ('&amp;', 0.3486)]</t>
         </is>
       </c>
       <c r="J164" t="n">
@@ -6698,24 +6749,24 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95%</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which language is spoken in Germany?.://www.google.com/url?sa=t&amp;source=web&amp;r</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1</v>
+        <v>0.424263209104538</v>
       </c>
       <c r="F165" t="n">
-        <v>1</v>
+        <v>0.9444428682327271</v>
       </c>
       <c r="G165" t="n">
-        <v>-0</v>
+        <v>0.5584724545478821</v>
       </c>
       <c r="H165" t="b">
         <v>1</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 1.0), ('sa', 1.0), ('=t', 0.6514), ('&amp;', 1.0), ('source', 1.0), ('=', 1.0), ('web', 1.0), ('&amp;r', 0.6514)]</t>
         </is>
       </c>
       <c r="J165" t="n">
@@ -6736,24 +6787,24 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95%</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which language is spoken in Germany?.://www.google.com/url?sa=t&amp;source=web&amp;</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1</v>
+        <v>0.2270916998386383</v>
       </c>
       <c r="F166" t="n">
-        <v>1</v>
+        <v>0.9058996438980103</v>
       </c>
       <c r="G166" t="n">
-        <v>-0</v>
+        <v>0.6466038227081299</v>
       </c>
       <c r="H166" t="b">
         <v>1</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 1.0), ('sa', 1.0), ('=t', 0.6514), ('&amp;', 1.0), ('source', 1.0), ('=', 1.0), ('web', 1.0), ('&amp;', 0.3486)]</t>
         </is>
       </c>
       <c r="J166" t="n">
@@ -6774,24 +6825,24 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95%</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which language is spoken in Germany?.://www.google.com/url?sa=t&amp;source=web&amp;r</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1</v>
+        <v>0.424263209104538</v>
       </c>
       <c r="F167" t="n">
-        <v>1</v>
+        <v>0.9444428682327271</v>
       </c>
       <c r="G167" t="n">
-        <v>-0</v>
+        <v>0.5584724545478821</v>
       </c>
       <c r="H167" t="b">
         <v>1</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 1.0), ('sa', 1.0), ('=t', 0.6514), ('&amp;', 1.0), ('source', 1.0), ('=', 1.0), ('web', 1.0), ('&amp;r', 0.6514)]</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -6812,24 +6863,24 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95%</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which language is spoken in Germany?.://www.google.com/url?sa=t&amp;source=web&amp;r</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1</v>
+        <v>0.424263209104538</v>
       </c>
       <c r="F168" t="n">
-        <v>1</v>
+        <v>0.9444428682327271</v>
       </c>
       <c r="G168" t="n">
-        <v>-0</v>
+        <v>0.5584724545478821</v>
       </c>
       <c r="H168" t="b">
         <v>1</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 1.0), ('sa', 1.0), ('=t', 0.6514), ('&amp;', 1.0), ('source', 1.0), ('=', 1.0), ('web', 1.0), ('&amp;r', 0.6514)]</t>
         </is>
       </c>
       <c r="J168" t="n">
@@ -6850,24 +6901,24 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95%</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which language is spoken in Germany?.://www.google.com/url?sa=t&amp;source=web&amp;r</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1</v>
+        <v>0.424263209104538</v>
       </c>
       <c r="F169" t="n">
-        <v>1</v>
+        <v>0.9444428682327271</v>
       </c>
       <c r="G169" t="n">
-        <v>-0</v>
+        <v>0.5584724545478821</v>
       </c>
       <c r="H169" t="b">
         <v>1</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 1.0), ('sa', 1.0), ('=t', 0.6514), ('&amp;', 1.0), ('source', 1.0), ('=', 1.0), ('web', 1.0), ('&amp;r', 0.6514)]</t>
         </is>
       </c>
       <c r="J169" t="n">
@@ -6888,24 +6939,24 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95%</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which language is spoken in Germany?.://www.google.com/url?sa=t&amp;source=web&amp;r</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1</v>
+        <v>0.424263209104538</v>
       </c>
       <c r="F170" t="n">
-        <v>1</v>
+        <v>0.9444428682327271</v>
       </c>
       <c r="G170" t="n">
-        <v>-0</v>
+        <v>0.5584724545478821</v>
       </c>
       <c r="H170" t="b">
         <v>1</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 1.0), ('sa', 1.0), ('=t', 0.6514), ('&amp;', 1.0), ('source', 1.0), ('=', 1.0), ('web', 1.0), ('&amp;r', 0.6514)]</t>
         </is>
       </c>
       <c r="J170" t="n">
@@ -6926,24 +6977,24 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95%</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which language is spoken in Germany?.://www.google.com/url?sa=t&amp;source=web&amp;</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1</v>
+        <v>0.2270916998386383</v>
       </c>
       <c r="F171" t="n">
-        <v>1</v>
+        <v>0.9058996438980103</v>
       </c>
       <c r="G171" t="n">
-        <v>-0</v>
+        <v>0.6466038227081299</v>
       </c>
       <c r="H171" t="b">
         <v>1</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?', 1.0), ('sa', 1.0), ('=t', 0.6514), ('&amp;', 1.0), ('source', 1.0), ('=', 1.0), ('web', 1.0), ('&amp;', 0.3486)]</t>
         </is>
       </c>
       <c r="J171" t="n">
@@ -6964,29 +7015,29 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the official language of China?.://en.wikipedia.org/wiki/China
+Given these facts:</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F172" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G172" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H172" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.3486), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('China', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -7003,29 +7054,29 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the official language of China?.://www.google.com/ is the official language of China.
+Given</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1</v>
+        <v>0.3256774246692657</v>
       </c>
       <c r="F173" t="n">
-        <v>1</v>
+        <v>0.9279384613037109</v>
       </c>
       <c r="G173" t="n">
-        <v>-0</v>
+        <v>0.6258097887039185</v>
       </c>
       <c r="H173" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 0.6514), ('.google', 1.0), ('.com', 1.0), ('/', 0.5), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('.\n', 1.0), ('Given', 1.0)]</t>
         </is>
       </c>
       <c r="J173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -7042,29 +7093,29 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the official language of China?.://en.wikipedia.org/wiki/China
+Given these facts:</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F174" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G174" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.3486), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('China', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -7081,29 +7132,28 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the official language of China?.://www.google.com/url?sa=U&amp;ved=0</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1</v>
+        <v>0.212131604552269</v>
       </c>
       <c r="F175" t="n">
-        <v>1</v>
+        <v>0.901793360710144</v>
       </c>
       <c r="G175" t="n">
-        <v>-0</v>
+        <v>0.9050459861755371</v>
       </c>
       <c r="H175" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 0.6514), ('.google', 1.0), ('.com', 1.0), ('/url', 0.5), ('?', 1.0), ('sa', 1.0), ('=', 0.6514), ('U', 1.0), ('&amp;', 1.0), ('ved', 1.0), ('=', 1.0), ('0', 1.0)]</t>
         </is>
       </c>
       <c r="J175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -7120,29 +7170,29 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the official language of China?.://en.wikipedia.org/wiki/China
+Given these facts:</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F176" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G176" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H176" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.3486), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('China', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -7159,29 +7209,29 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the official language of China?.://en.wikipedia.org/wiki/China
+Given these facts:</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F177" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G177" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H177" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.3486), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('China', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -7198,29 +7248,29 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the official language of China?.://en.wikipedia.org/wiki/China
+Given these facts:</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F178" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G178" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H178" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.3486), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('China', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -7237,29 +7287,28 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the official language of China?.://www.google.com/url?sa=U&amp;ved=0</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1</v>
+        <v>0.212131604552269</v>
       </c>
       <c r="F179" t="n">
-        <v>1</v>
+        <v>0.901793360710144</v>
       </c>
       <c r="G179" t="n">
-        <v>-0</v>
+        <v>0.9050459861755371</v>
       </c>
       <c r="H179" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 0.6514), ('.google', 1.0), ('.com', 1.0), ('/url', 0.5), ('?', 1.0), ('sa', 1.0), ('=', 0.6514), ('U', 1.0), ('&amp;', 1.0), ('ved', 1.0), ('=', 1.0), ('0', 1.0)]</t>
         </is>
       </c>
       <c r="J179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -7276,29 +7325,29 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the official language of China?.://en.wikipedia.org/wiki/China
+Given these facts:</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F180" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G180" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H180" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.3486), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('China', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -7315,29 +7364,29 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the official language of China?.://www.google.com/ is the official language of China.
+Given</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1</v>
+        <v>0.3256774246692657</v>
       </c>
       <c r="F181" t="n">
-        <v>1</v>
+        <v>0.9279384613037109</v>
       </c>
       <c r="G181" t="n">
-        <v>-0</v>
+        <v>0.6258097887039185</v>
       </c>
       <c r="H181" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 0.6514), ('.google', 1.0), ('.com', 1.0), ('/', 0.5), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('.\n', 1.0), ('Given', 1.0)]</t>
         </is>
       </c>
       <c r="J181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -7354,27 +7403,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple
-Which company developed the iPhone?
-Apple developed the iPhone.
-What is</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which company developed the iPhone?.://www.apple.com
+Given these facts: 1) Paris</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>0.424263209104538</v>
+        <v>1</v>
       </c>
       <c r="F182" t="n">
-        <v>0.9444428682327271</v>
+        <v>1</v>
       </c>
       <c r="G182" t="n">
-        <v>0.5584724545478821</v>
+        <v>-0</v>
       </c>
       <c r="H182" t="b">
         <v>1</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), ('\n', 0.6514), ('Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('Apple', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.\n', 1.0), ('What', 0.6514), (' is', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.apple', 1.0), ('.com', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0), (' Paris', 1.0)]</t>
         </is>
       </c>
       <c r="J182" t="n">
@@ -7395,27 +7442,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple
-Which company developed the iPhone?
-Apple developed the iPhone.
-What is</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which company developed the iPhone?.://www.apple.com
+Given these facts: 1) Paris</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>0.424263209104538</v>
+        <v>1</v>
       </c>
       <c r="F183" t="n">
-        <v>0.9444428682327271</v>
+        <v>1</v>
       </c>
       <c r="G183" t="n">
-        <v>0.5584724545478821</v>
+        <v>-0</v>
       </c>
       <c r="H183" t="b">
         <v>1</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), ('\n', 0.6514), ('Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('Apple', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.\n', 1.0), ('What', 0.6514), (' is', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.apple', 1.0), ('.com', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0), (' Paris', 1.0)]</t>
         </is>
       </c>
       <c r="J183" t="n">
@@ -7436,27 +7481,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple
-Which company developed the iPhone?
-Apple developed the iPhone.
-The iPhone</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which company developed the iPhone?.://www.apple.com
+Given these facts: 1) Paris</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>0.2270916998386383</v>
+        <v>1</v>
       </c>
       <c r="F184" t="n">
-        <v>0.9058996438980103</v>
+        <v>1</v>
       </c>
       <c r="G184" t="n">
-        <v>0.6466038227081299</v>
+        <v>-0</v>
       </c>
       <c r="H184" t="b">
         <v>1</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), ('\n', 0.6514), ('Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('Apple', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.\n', 1.0), ('The', 0.3486), (' iPhone', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.apple', 1.0), ('.com', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0), (' Paris', 1.0)]</t>
         </is>
       </c>
       <c r="J184" t="n">
@@ -7477,27 +7520,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple
-Which company developed the iPhone?
-Apple developed the iPhone.
-The iPhone</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which company developed the iPhone?.://www.apple.com
+Given these facts: 1) Paris</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>0.2270916998386383</v>
+        <v>1</v>
       </c>
       <c r="F185" t="n">
-        <v>0.9058996438980103</v>
+        <v>1</v>
       </c>
       <c r="G185" t="n">
-        <v>0.6466038227081299</v>
+        <v>-0</v>
       </c>
       <c r="H185" t="b">
         <v>1</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), ('\n', 0.6514), ('Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('Apple', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.\n', 1.0), ('The', 0.3486), (' iPhone', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.apple', 1.0), ('.com', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0), (' Paris', 1.0)]</t>
         </is>
       </c>
       <c r="J185" t="n">
@@ -7518,24 +7559,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple Inc. is an American multinational technology company headquartered in Cupertino, California,</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which company developed the iPhone?.://www.apple.com
+Given these facts: 1) Paris</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="F186" t="n">
-        <v>0.9321638345718384</v>
+        <v>1</v>
       </c>
       <c r="G186" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="H186" t="b">
         <v>1</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), (' Inc', 0.3486), ('.', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' headquartered', 1.0), (' in', 1.0), (' Cupertino', 1.0), (',', 1.0), (' California', 1.0), (',', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.apple', 1.0), ('.com', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0), (' Paris', 1.0)]</t>
         </is>
       </c>
       <c r="J186" t="n">
@@ -7556,27 +7598,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple
-Which company developed the iPhone?
-Apple developed the iPhone.
-The iPhone</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which company developed the iPhone?.://www.apple.com
+Given these facts: 1) Paris</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>0.2270916998386383</v>
+        <v>1</v>
       </c>
       <c r="F187" t="n">
-        <v>0.9058996438980103</v>
+        <v>1</v>
       </c>
       <c r="G187" t="n">
-        <v>0.6466038227081299</v>
+        <v>-0</v>
       </c>
       <c r="H187" t="b">
         <v>1</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), ('\n', 0.6514), ('Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('Apple', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.\n', 1.0), ('The', 0.3486), (' iPhone', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.apple', 1.0), ('.com', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0), (' Paris', 1.0)]</t>
         </is>
       </c>
       <c r="J187" t="n">
@@ -7597,24 +7637,25 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple Inc. is an American multinational technology company headquartered in Cupertino, California,</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which company developed the iPhone?.://www.apple.com
+Given these facts: 1) Paris</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="F188" t="n">
-        <v>0.9321638345718384</v>
+        <v>1</v>
       </c>
       <c r="G188" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="H188" t="b">
         <v>1</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), (' Inc', 0.3486), ('.', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' headquartered', 1.0), (' in', 1.0), (' Cupertino', 1.0), (',', 1.0), (' California', 1.0), (',', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.apple', 1.0), ('.com', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0), (' Paris', 1.0)]</t>
         </is>
       </c>
       <c r="J188" t="n">
@@ -7635,24 +7676,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple Inc. is an American multinational technology company headquartered in Cupertino, California,</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which company developed the iPhone?.://www.apple.com
+Given these facts: 1) Paris</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="F189" t="n">
-        <v>0.9321638345718384</v>
+        <v>1</v>
       </c>
       <c r="G189" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="H189" t="b">
         <v>1</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), (' Inc', 0.3486), ('.', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' headquartered', 1.0), (' in', 1.0), (' Cupertino', 1.0), (',', 1.0), (' California', 1.0), (',', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.apple', 1.0), ('.com', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0), (' Paris', 1.0)]</t>
         </is>
       </c>
       <c r="J189" t="n">
@@ -7673,24 +7715,25 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple Inc. is an American multinational technology company headquartered in Cupertino, California,</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which company developed the iPhone?.://www.apple.com
+Given these facts: 1) Paris</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="F190" t="n">
-        <v>0.9321638345718384</v>
+        <v>1</v>
       </c>
       <c r="G190" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="H190" t="b">
         <v>1</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), (' Inc', 0.3486), ('.', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' headquartered', 1.0), (' in', 1.0), (' Cupertino', 1.0), (',', 1.0), (' California', 1.0), (',', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.apple', 1.0), ('.com', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0), (' Paris', 1.0)]</t>
         </is>
       </c>
       <c r="J190" t="n">
@@ -7711,27 +7754,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple
-Which company developed the iPhone?
-Apple developed the iPhone.
-The iPhone</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which company developed the iPhone?.://www.apple.com
+Given these facts: 1) Paris</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>0.2270916998386383</v>
+        <v>1</v>
       </c>
       <c r="F191" t="n">
-        <v>0.9058996438980103</v>
+        <v>1</v>
       </c>
       <c r="G191" t="n">
-        <v>0.6466038227081299</v>
+        <v>-0</v>
       </c>
       <c r="H191" t="b">
         <v>1</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), ('\n', 0.6514), ('Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('Apple', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.\n', 1.0), ('The', 0.3486), (' iPhone', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.apple', 1.0), ('.com', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0), (' Paris', 1.0)]</t>
         </is>
       </c>
       <c r="J191" t="n">
@@ -7752,29 +7793,29 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the name of the online retailer founded by Jeff Bezos?.://
+Given these facts: 1) Paris is the capital</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F192" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G192" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H192" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('\n', 0.6514), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0), (' Paris', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0)]</t>
         </is>
       </c>
       <c r="J192" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="193">
@@ -7791,29 +7832,29 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the name of the online retailer founded by Jeff Bezos?.://span&gt;Amazon.com
+Given these facts: 1)</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F193" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G193" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H193" t="b">
         <v>1</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('span', 0.3486), ('&gt;', 1.0), ('Amazon', 1.0), ('.com', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0)]</t>
         </is>
       </c>
       <c r="J193" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="194">
@@ -7830,29 +7871,29 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the name of the online retailer founded by Jeff Bezos?.://
+Given these facts: 1) Paris is the capital</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F194" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G194" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H194" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('\n', 0.6514), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0), (' Paris', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0)]</t>
         </is>
       </c>
       <c r="J194" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="195">
@@ -7869,29 +7910,29 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the name of the online retailer founded by Jeff Bezos?.://
+Given these facts: 1) Paris is the capital</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F195" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G195" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H195" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('\n', 0.6514), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0), (' Paris', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0)]</t>
         </is>
       </c>
       <c r="J195" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="196">
@@ -7908,29 +7949,29 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the name of the online retailer founded by Jeff Bezos?.://span&gt;Amazon.com
+Given these facts: 1)</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F196" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G196" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H196" t="b">
         <v>1</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('span', 0.3486), ('&gt;', 1.0), ('Amazon', 1.0), ('.com', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0)]</t>
         </is>
       </c>
       <c r="J196" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="197">
@@ -7947,29 +7988,29 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the name of the online retailer founded by Jeff Bezos?.://
+Given these facts: 1) Paris is the capital</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F197" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G197" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H197" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('\n', 0.6514), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0), (' Paris', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0)]</t>
         </is>
       </c>
       <c r="J197" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="198">
@@ -7986,29 +8027,29 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the name of the online retailer founded by Jeff Bezos?.://span&gt;Amazon.com
+Given these facts: 1)</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F198" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G198" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H198" t="b">
         <v>1</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('span', 0.3486), ('&gt;', 1.0), ('Amazon', 1.0), ('.com', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0)]</t>
         </is>
       </c>
       <c r="J198" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="199">
@@ -8025,29 +8066,29 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the name of the online retailer founded by Jeff Bezos?.://span&gt;Amazon.com
+Given these facts: 1)</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F199" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G199" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H199" t="b">
         <v>1</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('span', 0.3486), ('&gt;', 1.0), ('Amazon', 1.0), ('.com', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0)]</t>
         </is>
       </c>
       <c r="J199" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="200">
@@ -8064,29 +8105,29 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the name of the online retailer founded by Jeff Bezos?.://
+Given these facts: 1) Paris is the capital</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F200" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G200" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H200" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('\n', 0.6514), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0), (' Paris', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0)]</t>
         </is>
       </c>
       <c r="J200" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="201">
@@ -8103,29 +8144,29 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: What is the name of the online retailer founded by Jeff Bezos?.://span&gt;Amazon.com
+Given these facts: 1)</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F201" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G201" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H201" t="b">
         <v>1</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('span', 0.3486), ('&gt;', 1.0), ('Amazon', 1.0), ('.com', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0)]</t>
         </is>
       </c>
       <c r="J201" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="202">
@@ -8142,9 +8183,8 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which company is known for its search engine?.://www.google.com
+Given these facts: 1) Paris</t>
         </is>
       </c>
       <c r="E202" t="n">
@@ -8161,7 +8201,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0), (' Paris', 1.0)]</t>
         </is>
       </c>
       <c r="J202" t="n">
@@ -8182,9 +8222,8 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which company is known for its search engine?.://www.google.com
+Given these facts: 1) Paris</t>
         </is>
       </c>
       <c r="E203" t="n">
@@ -8201,7 +8240,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0), (' Paris', 1.0)]</t>
         </is>
       </c>
       <c r="J203" t="n">
@@ -8222,9 +8261,8 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which company is known for its search engine?.://www.google.com
+Given these facts: 1) Paris</t>
         </is>
       </c>
       <c r="E204" t="n">
@@ -8241,7 +8279,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0), (' Paris', 1.0)]</t>
         </is>
       </c>
       <c r="J204" t="n">
@@ -8262,9 +8300,8 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which company is known for its search engine?.://www.google.com
+Given these facts: 1) Paris</t>
         </is>
       </c>
       <c r="E205" t="n">
@@ -8281,7 +8318,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0), (' Paris', 1.0)]</t>
         </is>
       </c>
       <c r="J205" t="n">
@@ -8302,9 +8339,8 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which company is known for its search engine?.://www.google.com
+Given these facts: 1) Paris</t>
         </is>
       </c>
       <c r="E206" t="n">
@@ -8321,7 +8357,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0), (' Paris', 1.0)]</t>
         </is>
       </c>
       <c r="J206" t="n">
@@ -8342,9 +8378,8 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which company is known for its search engine?.://www.google.com
+Given these facts: 1) Paris</t>
         </is>
       </c>
       <c r="E207" t="n">
@@ -8361,7 +8396,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0), (' Paris', 1.0)]</t>
         </is>
       </c>
       <c r="J207" t="n">
@@ -8382,9 +8417,8 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which company is known for its search engine?.://www.google.com
+Given these facts: 1) Paris</t>
         </is>
       </c>
       <c r="E208" t="n">
@@ -8401,7 +8435,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0), (' Paris', 1.0)]</t>
         </is>
       </c>
       <c r="J208" t="n">
@@ -8422,9 +8456,8 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which company is known for its search engine?.://www.google.com
+Given these facts: 1) Paris</t>
         </is>
       </c>
       <c r="E209" t="n">
@@ -8441,7 +8474,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0), (' Paris', 1.0)]</t>
         </is>
       </c>
       <c r="J209" t="n">
@@ -8462,9 +8495,8 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which company is known for its search engine?.://www.google.com
+Given these facts: 1) Paris</t>
         </is>
       </c>
       <c r="E210" t="n">
@@ -8481,7 +8513,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0), (' Paris', 1.0)]</t>
         </is>
       </c>
       <c r="J210" t="n">
@@ -8502,9 +8534,8 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company</t>
+          <t>Given these facts: 1) Paris is the capital of France. 2) The Eiffel Tower is located in Paris. 3) French is the official language of France. Deduce the answer to the following: Which company is known for its search engine?.://www.google.com
+Given these facts: 1) Paris</t>
         </is>
       </c>
       <c r="E211" t="n">
@@ -8521,7 +8552,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('\n', 1.0), ('Given', 1.0), (' these', 1.0), (' facts', 1.0), (':', 1.0), (' ', 1.0), ('1', 1.0), (')', 1.0), (' Paris', 1.0)]</t>
         </is>
       </c>
       <c r="J211" t="n">
